--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_145_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_145_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2099</v>
+        <v>5.329</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1483</v>
+        <v>2.1665</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0617</v>
+        <v>3.1625</v>
       </c>
       <c r="G2" t="n">
         <v>2.4858</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2631</v>
+        <v>0.856</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>0.13</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6251</v>
+        <v>0.726</v>
       </c>
       <c r="V2" t="n">
         <v>3.6109</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7833</v>
+        <v>3.7008</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0074</v>
+        <v>2.0257</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7759</v>
+        <v>1.6751</v>
       </c>
       <c r="G3" t="n">
         <v>0.4158</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0242</v>
+        <v>0.8933</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8883</v>
+        <v>0.13</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8641</v>
+        <v>0.7633</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3103</v>
+        <v>2.2156</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6625</v>
+        <v>1.2654</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6478</v>
+        <v>0.9502</v>
       </c>
       <c r="G4" t="n">
         <v>1.5201</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3262</v>
+        <v>1.2316</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8338</v>
+        <v>0.4367</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4925</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36</v>
+        <v>1.3271</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5082</v>
+        <v>3.7441</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1482</v>
+        <v>-2.4171</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8648</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1362</v>
+        <v>-0.1691</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U5" t="n">
-        <v>0.536</v>
+        <v>0.2671</v>
       </c>
       <c r="V5" t="n">
         <v>3.7527</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1901</v>
+        <v>0.9506</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0886</v>
+        <v>0.9025</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2787</v>
+        <v>0.0481</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9613</v>
+        <v>-0.5952</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.228</v>
+        <v>0.6627</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7332</v>
+        <v>-1.2579</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9892</v>
+        <v>1.4847</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1526</v>
+        <v>1.2639</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8366</v>
+        <v>0.2208</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9721</v>
+        <v>-2.0799</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0755</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8966</v>
+        <v>-1.4787</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5277</v>
+        <v>1.0251</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9006</v>
+        <v>0.4485</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6272</v>
+        <v>0.5766</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8766</v>
+        <v>0.5592</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0637</v>
+        <v>1.5853</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1871</v>
+        <v>-1.026</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5952</v>
+        <v>-1.2719</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6627</v>
+        <v>0.0396</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2579</v>
+        <v>-1.3115</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4847</v>
+        <v>0.4367</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2639</v>
+        <v>1.1126</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2208</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0799</v>
+        <v>-1.7086</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6012</v>
+        <v>-1.073</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4787</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7112</v>
+        <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.3646</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6097</v>
+        <v>0.0042</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3413</v>
+        <v>0.3605</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1444</v>
+        <v>1.4665</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6805</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4419</v>
+        <v>0.1209</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7032</v>
+        <v>-1.4857</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2613</v>
+        <v>1.6066</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2719</v>
+        <v>-2.9613</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0396</v>
+        <v>-1.228</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3115</v>
+        <v>-1.7332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4367</v>
+        <v>-1.9892</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1126</v>
+        <v>-1.1526</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.8366</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7086</v>
+        <v>-0.9721</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.073</v>
+        <v>-0.0755</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2473</v>
+        <v>1.4585</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1221</v>
+        <v>0.5034</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1252</v>
+        <v>0.955</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4665</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5168</v>
+        <v>-0.6901</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8106</v>
+        <v>-0.956</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3274</v>
+        <v>0.266</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6815</v>
+        <v>-0.7076</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.976</v>
+        <v>-0.4969</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2944</v>
+        <v>-0.2108</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0342</v>
+        <v>-0.7359</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0539</v>
+        <v>0.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9802999999999999</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7157</v>
+        <v>0.0283</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0299</v>
+        <v>-0.5473</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>0.5756</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1801</v>
+        <v>0.2495</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4876</v>
+        <v>0.0119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3075</v>
+        <v>0.2377</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5899</v>
+        <v>-0.7362</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1919</v>
+        <v>0.4568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.602</v>
+        <v>-1.1929</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7076</v>
+        <v>-0.6815</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4969</v>
+        <v>-0.976</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2108</v>
+        <v>0.2944</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7359</v>
+        <v>1.0342</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0504</v>
+        <v>0.0539</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7863</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0283</v>
+        <v>-1.7157</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5473</v>
+        <v>-1.0299</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5756</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3497</v>
+        <v>-0.0393</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>0.1338</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5737</v>
+        <v>-0.1731</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8582</v>
+        <v>-3.5666</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8028</v>
+        <v>-1.7464</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0555</v>
+        <v>-1.8202</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8172</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.959</v>
+        <v>0.2506</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1246</v>
+        <v>0.181</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1656</v>
+        <v>0.0696</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.239</v>
+        <v>-4.8686</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5903</v>
+        <v>-2.3544</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6487</v>
+        <v>-2.5143</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3104</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7714</v>
+        <v>-0.4011</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.174</v>
+        <v>-0.0395</v>
       </c>
       <c r="V12" t="n">
         <v>0.3943</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.968199999999999</v>
+        <v>4.3417</v>
       </c>
       <c r="E13" t="n">
-        <v>5.230300000000001</v>
+        <v>5.603799999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2621</v>
+        <v>-1.261999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.788200000000001</v>
+        <v>-5.7882</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7181</v>
+        <v>-4.718099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.070200000000001</v>
+        <v>-1.0702</v>
       </c>
       <c r="J13" t="n">
         <v>7.990399999999998</v>
@@ -1447,7 +1447,7 @@
         <v>1.9183</v>
       </c>
       <c r="L13" t="n">
-        <v>6.072099999999999</v>
+        <v>6.0721</v>
       </c>
       <c r="M13" t="n">
         <v>-13.779</v>
@@ -1459,7 +1459,7 @@
         <v>-7.1423</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.9587</v>
+        <v>-6.958699999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.3964</v>
@@ -1468,13 +1468,13 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3462</v>
+        <v>5.7197</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8082000000000001</v>
+        <v>1.1818</v>
       </c>
       <c r="U13" t="n">
-        <v>4.537999999999998</v>
+        <v>4.538100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>11.3688</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9068</v>
+        <v>5.3</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0927</v>
+        <v>5.3286</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1859</v>
+        <v>-0.0286</v>
       </c>
       <c r="G14" t="n">
         <v>3.6565</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6054</v>
+        <v>-0.2122</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8804</v>
+        <v>-0.6445</v>
       </c>
       <c r="U14" t="n">
-        <v>0.275</v>
+        <v>0.4323</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9731</v>
+        <v>1.8989</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5926</v>
+        <v>2.5515</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3805</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3524</v>
+        <v>2.1567</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6062</v>
+        <v>1.6783</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7461</v>
+        <v>0.4785</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8914</v>
+        <v>2.8147</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3025</v>
+        <v>1.6504</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5889</v>
+        <v>1.1643</v>
       </c>
       <c r="M15" t="n">
-        <v>0.461</v>
+        <v>-0.658</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3038</v>
+        <v>0.0279</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>-0.6859</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3071</v>
+        <v>-0.2732</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2987</v>
+        <v>-0.2631</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0083</v>
+        <v>-0.0101</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1239</v>
+        <v>1.8723</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8438</v>
+        <v>0.5926</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7199</v>
+        <v>1.2797</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1567</v>
+        <v>1.3524</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6783</v>
+        <v>0.6062</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4785</v>
+        <v>0.7461</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8147</v>
+        <v>0.8914</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6504</v>
+        <v>0.3025</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1643</v>
+        <v>0.5889</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.658</v>
+        <v>0.461</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0279</v>
+        <v>0.3038</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6859</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0482</v>
+        <v>-0.4079</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9709</v>
+        <v>-0.2987</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.1092</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0272</v>
+        <v>1.4889</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.192</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9269</v>
+        <v>1.6809</v>
       </c>
       <c r="G17" t="n">
         <v>0.5339</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7723</v>
+        <v>-0.3106</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3443</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.572</v>
+        <v>0.326</v>
       </c>
       <c r="V17" t="n">
         <v>1.4975</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2959</v>
+        <v>0.9915</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6219</v>
+        <v>1.8578</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.326</v>
+        <v>-0.8662</v>
       </c>
       <c r="G18" t="n">
         <v>1.0392</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6891</v>
+        <v>-0.9935</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1044</v>
+        <v>-0.8685</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5847</v>
+        <v>-0.125</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6778999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2283</v>
+        <v>-0.5182</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0516</v>
+        <v>-0.4585</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1767</v>
+        <v>-0.0598</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4277</v>
+        <v>3.7011</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1043</v>
+        <v>3.5772</v>
       </c>
       <c r="I19" t="n">
-        <v>0.532</v>
+        <v>0.1239</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2405</v>
+        <v>3.2329</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6687</v>
+        <v>3.1593</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4282</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6681</v>
+        <v>0.4681</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5644</v>
+        <v>0.4179</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1038</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2385</v>
+        <v>-0.5957</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1889</v>
+        <v>-0.2122</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0496</v>
+        <v>-0.3835</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.762</v>
+        <v>-1.0025</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.053</v>
+        <v>-0.5234</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.709</v>
+        <v>-0.4791</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7792</v>
+        <v>0.4277</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8295</v>
+        <v>-0.1043</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0502</v>
+        <v>0.532</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1261</v>
+        <v>-0.2405</v>
       </c>
       <c r="K20" t="n">
-        <v>0.39</v>
+        <v>-0.6687</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7361</v>
+        <v>0.4282</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9053</v>
+        <v>0.6681</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2195</v>
+        <v>0.5644</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>0.1038</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0868</v>
+        <v>-0.5357</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1404</v>
+        <v>-0.2829</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0536</v>
+        <v>-0.2528</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1418</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8214</v>
+        <v>-1.3632</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6944</v>
+        <v>-0.8786</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.127</v>
+        <v>-0.4845</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7011</v>
+        <v>-0.7792</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5772</v>
+        <v>-0.8295</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1239</v>
+        <v>0.0502</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2329</v>
+        <v>1.1261</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1593</v>
+        <v>0.39</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>0.7361</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4681</v>
+        <v>-1.9053</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4179</v>
+        <v>-1.2195</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0502</v>
+        <v>-0.6859</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.5515</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8988</v>
+        <v>0.4856</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>0.3148</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4507</v>
+        <v>0.1709</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9813</v>
+        <v>-1.8805</v>
       </c>
       <c r="E22" t="n">
         <v>-1.2681</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.688</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8448</v>
+        <v>-0.744</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6563</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1885</v>
+        <v>-0.0876</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9906</v>
+        <v>-2.4617</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3943</v>
+        <v>-2.6302</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4037</v>
+        <v>0.1685</v>
       </c>
       <c r="G23" t="n">
         <v>-0.349</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4793</v>
+        <v>-0.9504</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.8685</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1533</v>
+        <v>-0.0819</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9304</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5117</v>
+        <v>-7.5074</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.528</v>
+        <v>-3.1178</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9837</v>
+        <v>-4.3896</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2631</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0268</v>
+        <v>-0.0224</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4683</v>
+        <v>-0.1215</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4951</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-5.0774</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.968400000000002</v>
+        <v>-3.1819</v>
       </c>
       <c r="E25" t="n">
-        <v>1.261899999999999</v>
+        <v>1.261899999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2303</v>
+        <v>-4.4438</v>
       </c>
       <c r="G25" t="n">
         <v>5.7882</v>
@@ -2404,13 +2404,13 @@
         <v>17.3965</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.346500000000001</v>
+        <v>-4.56</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.5381</v>
+        <v>-4.538</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8083</v>
+        <v>-0.02180000000000003</v>
       </c>
       <c r="V25" t="n">
         <v>-11.3689</v>
